--- a/output_4a.xlsx
+++ b/output_4a.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>364256</v>
+        <v>364253.3</v>
       </c>
     </row>
     <row r="4">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1023.33</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12420</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="6">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>520699.33</v>
+        <v>520723.3</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.33</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.279999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>902.3</v>
+        <v>902</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10828</v>
+        <v>10830</v>
       </c>
     </row>
   </sheetData>
@@ -586,10 +586,10 @@
         <v>30000</v>
       </c>
       <c r="D2" t="n">
-        <v>43070</v>
+        <v>43156</v>
       </c>
       <c r="E2" t="n">
-        <v>73070</v>
+        <v>73156</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -607,10 +607,10 @@
         <v>17500</v>
       </c>
       <c r="D3" t="n">
-        <v>23474.5</v>
+        <v>23477.3</v>
       </c>
       <c r="E3" t="n">
-        <v>40974.5</v>
+        <v>40977.3</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -712,10 +712,10 @@
         <v>27000</v>
       </c>
       <c r="D8" t="n">
-        <v>142351.5</v>
+        <v>142260</v>
       </c>
       <c r="E8" t="n">
-        <v>169351.5</v>
+        <v>169260</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -733,16 +733,16 @@
         <v>143000</v>
       </c>
       <c r="D9" t="n">
-        <v>364256</v>
+        <v>364253.3</v>
       </c>
       <c r="E9" t="n">
-        <v>507256</v>
+        <v>507253.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1023.33</v>
+        <v>1020</v>
       </c>
       <c r="G9" t="n">
-        <v>12420</v>
+        <v>12450</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3609.3</v>
+        <v>3602</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -935,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="G2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="H2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="I2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -953,16 +953,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="M2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="N2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="O2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -971,13 +971,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="S2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="T2" t="n">
-        <v>3609.3</v>
+        <v>3610</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3507</v>
+        <v>3500</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1044,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5414</v>
+        <v>5409</v>
       </c>
       <c r="K3" t="n">
-        <v>5414</v>
+        <v>5415</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1062,10 +1062,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5414</v>
+        <v>5409</v>
       </c>
       <c r="Q3" t="n">
-        <v>5414</v>
+        <v>5415</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2707</v>
+        <v>2721</v>
       </c>
       <c r="V3" t="n">
-        <v>5414</v>
+        <v>5415</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3353.5</v>
+        <v>3350</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5414</v>
+        <v>5412</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5414</v>
+        <v>5412</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4060.5</v>
+        <v>4068</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>13600</v>
       </c>
       <c r="C5" t="n">
-        <v>13137.2</v>
+        <v>13125</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>18949</v>
+        <v>18942</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>18949</v>
+        <v>18942</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>14211.8</v>
+        <v>14238</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2502.3</v>
+        <v>2500</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3609.3</v>
+        <v>3608</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3609.3</v>
+        <v>3608</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2707</v>
+        <v>2712</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>2400</v>
       </c>
       <c r="H7" t="n">
-        <v>1876.8</v>
+        <v>1875</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2030.2</v>
+        <v>2034</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>800</v>
       </c>
       <c r="J8" t="n">
-        <v>625.6</v>
+        <v>625</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>902.3</v>
+        <v>902</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>902.3</v>
+        <v>902</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>676.8</v>
+        <v>678</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1885,55 +1885,55 @@
         <v>6400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>3609.3</v>
+        <v>3612</v>
       </c>
       <c r="K2" t="n">
-        <v>7218.7</v>
+        <v>7222</v>
       </c>
       <c r="L2" t="n">
-        <v>10828</v>
+        <v>10832</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>3609.3</v>
+        <v>3620</v>
       </c>
       <c r="Q2" t="n">
-        <v>7218.7</v>
+        <v>7230</v>
       </c>
       <c r="R2" t="n">
-        <v>10828</v>
+        <v>10840</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V2" t="n">
-        <v>3609.3</v>
+        <v>3628</v>
       </c>
       <c r="W2" t="n">
-        <v>7218.7</v>
+        <v>7238</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5414</v>
+        <v>5409</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5414</v>
+        <v>5409</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2707</v>
+        <v>2721</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -2479,55 +2479,55 @@
         <v>1078</v>
       </c>
       <c r="K8" t="n">
-        <v>1458.6</v>
+        <v>1458</v>
       </c>
       <c r="L8" t="n">
-        <v>1250.6</v>
+        <v>1250</v>
       </c>
       <c r="M8" t="n">
-        <v>1072.6</v>
+        <v>1072</v>
       </c>
       <c r="N8" t="n">
-        <v>904.6</v>
+        <v>904</v>
       </c>
       <c r="O8" t="n">
-        <v>696.6</v>
+        <v>696</v>
       </c>
       <c r="P8" t="n">
-        <v>523.6</v>
+        <v>523</v>
       </c>
       <c r="Q8" t="n">
-        <v>1257.9</v>
+        <v>1257</v>
       </c>
       <c r="R8" t="n">
-        <v>1076.9</v>
+        <v>1076</v>
       </c>
       <c r="S8" t="n">
-        <v>888.9</v>
+        <v>888</v>
       </c>
       <c r="T8" t="n">
-        <v>676.9</v>
+        <v>676</v>
       </c>
       <c r="U8" t="n">
-        <v>423.9</v>
+        <v>423</v>
       </c>
       <c r="V8" t="n">
-        <v>204.9</v>
+        <v>204</v>
       </c>
       <c r="W8" t="n">
-        <v>911.2</v>
+        <v>910</v>
       </c>
       <c r="X8" t="n">
-        <v>685.2</v>
+        <v>684</v>
       </c>
       <c r="Y8" t="n">
-        <v>446.2</v>
+        <v>445</v>
       </c>
       <c r="Z8" t="n">
-        <v>226.2</v>
+        <v>225</v>
       </c>
       <c r="AA8" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="AB8" t="n">
         <v>521</v>
